--- a/data/trans_dic/P22$concerIndv-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P22$concerIndv-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menor, es beneficiaria de Seguro Médico concertado individualmente</t>
+          <t>Población que, al menos, es beneficiaria de seguro médico concertado individualmente (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,82; 3,19</t>
+          <t>0,82; 3,07</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,42; 2,35</t>
+          <t>0,42; 2,39</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,24; 6,23</t>
+          <t>2,2; 6,34</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,31; 8,69</t>
+          <t>1,25; 8,92</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,6; 4,69</t>
+          <t>1,48; 4,65</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,0; 5,67</t>
+          <t>2,0; 5,63</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,49; 4,88</t>
+          <t>1,51; 4,8</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,45; 9,89</t>
+          <t>2,6; 9,93</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,4; 3,28</t>
+          <t>1,41; 3,22</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,32; 3,38</t>
+          <t>1,4; 3,45</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,22; 4,84</t>
+          <t>2,22; 4,79</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,44; 7,62</t>
+          <t>2,64; 7,91</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,05; 2,95</t>
+          <t>1,01; 2,98</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,7; 6,26</t>
+          <t>2,63; 5,98</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,47; 4,28</t>
+          <t>1,52; 4,35</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,75; 6,41</t>
+          <t>1,65; 6,3</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,66; 7,27</t>
+          <t>3,53; 6,9</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,07; 6,48</t>
+          <t>2,97; 6,28</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,41; 10,91</t>
+          <t>6,0; 10,69</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,76; 12,92</t>
+          <t>5,81; 12,81</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,55; 4,52</t>
+          <t>2,52; 4,49</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3,1; 5,51</t>
+          <t>3,12; 5,49</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4,2; 7,01</t>
+          <t>4,24; 6,8</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,82; 8,97</t>
+          <t>4,73; 8,8</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,71; 5,75</t>
+          <t>2,74; 5,96</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,84; 7,57</t>
+          <t>3,59; 7,33</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,92; 7,49</t>
+          <t>3,93; 7,75</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,46; 11,57</t>
+          <t>6,67; 11,84</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,87; 6,18</t>
+          <t>2,92; 6,3</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,17; 4,96</t>
+          <t>2,18; 5,18</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,76; 7,56</t>
+          <t>3,85; 7,46</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,98; 10,82</t>
+          <t>6,99; 11,05</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,2; 5,33</t>
+          <t>3,18; 5,47</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3,27; 5,53</t>
+          <t>3,17; 5,56</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4,28; 6,83</t>
+          <t>4,23; 6,75</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7,31; 10,6</t>
+          <t>7,37; 10,58</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,54; 6,35</t>
+          <t>2,64; 6,28</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,67; 4,5</t>
+          <t>1,75; 4,51</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,28; 5,51</t>
+          <t>2,31; 5,62</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,81; 9,56</t>
+          <t>2,71; 9,55</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,38; 6,01</t>
+          <t>2,34; 5,72</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,79; 6,33</t>
+          <t>2,6; 6,04</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,67; 5,97</t>
+          <t>2,82; 5,96</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9,0; 13,13</t>
+          <t>8,9; 13,19</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,88; 5,36</t>
+          <t>2,84; 5,4</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,54; 4,78</t>
+          <t>2,51; 4,73</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,89; 5,23</t>
+          <t>2,86; 5,18</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5,1; 10,62</t>
+          <t>5,34; 10,77</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,4; 6,6</t>
+          <t>2,24; 6,9</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,44; 5,62</t>
+          <t>1,37; 5,28</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,08; 3,99</t>
+          <t>1,23; 4,41</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,92; 9,21</t>
+          <t>4,86; 8,91</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,75; 8,94</t>
+          <t>4,02; 9,09</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,21; 6,41</t>
+          <t>2,05; 6,25</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,88; 5,83</t>
+          <t>1,99; 5,8</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>7,32; 10,89</t>
+          <t>7,24; 10,78</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,71; 6,91</t>
+          <t>3,77; 6,96</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2,11; 5,09</t>
+          <t>2,11; 4,94</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,86; 4,41</t>
+          <t>1,89; 4,21</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,7; 9,3</t>
+          <t>6,5; 9,32</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,24</t>
+          <t>0,0; 3,29</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,36; 5,87</t>
+          <t>1,3; 5,71</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,05; 4,98</t>
+          <t>0,95; 4,68</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5,39; 9,8</t>
+          <t>5,3; 9,85</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,42; 4,91</t>
+          <t>1,43; 5,24</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,53; 3,47</t>
+          <t>0,55; 4,0</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,55; 5,92</t>
+          <t>1,38; 5,52</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,6; 6,37</t>
+          <t>1,69; 6,61</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,99; 3,17</t>
+          <t>0,98; 3,29</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1,26; 3,81</t>
+          <t>1,22; 3,73</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1,69; 4,31</t>
+          <t>1,69; 4,5</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2,56; 7,06</t>
+          <t>2,39; 7,12</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,46; 5,03</t>
+          <t>0,45; 4,71</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,42; 4,83</t>
+          <t>0,43; 5,64</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,4</t>
+          <t>0,0; 3,14</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,96; 5,49</t>
+          <t>1,85; 5,38</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,34; 2,85</t>
+          <t>0,34; 2,92</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,27; 3,09</t>
+          <t>0,27; 2,45</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,67; 4,44</t>
+          <t>0,68; 4,23</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,75; 5,46</t>
+          <t>2,75; 5,55</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,61; 2,97</t>
+          <t>0,59; 3,01</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,51; 3,03</t>
+          <t>0,65; 2,86</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,68; 3,12</t>
+          <t>0,62; 2,94</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,75; 4,84</t>
+          <t>2,74; 4,83</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,31; 3,4</t>
+          <t>2,27; 3,43</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,66; 3,95</t>
+          <t>2,62; 3,97</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,75; 4,09</t>
+          <t>2,76; 4,03</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4,66; 7,06</t>
+          <t>4,78; 7,09</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>3,28; 4,66</t>
+          <t>3,28; 4,7</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,71; 4,05</t>
+          <t>2,71; 4,08</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,77; 5,25</t>
+          <t>3,74; 5,18</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>6,27; 8,7</t>
+          <t>6,25; 8,7</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2,9; 3,82</t>
+          <t>2,97; 3,85</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2,87; 3,74</t>
+          <t>2,87; 3,76</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3,48; 4,45</t>
+          <t>3,47; 4,43</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>5,97; 7,6</t>
+          <t>5,93; 7,67</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menor, es beneficiaria de Seguro Médico concertado individualmente</t>
+          <t>Población que, al menos, es beneficiaria de seguro médico concertado individualmente (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4040; 15755</t>
+          <t>4066; 15116</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1884; 10668</t>
+          <t>1894; 10812</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9354; 25998</t>
+          <t>9201; 26461</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5251; 34752</t>
+          <t>5013; 35670</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>7501; 21938</t>
+          <t>6929; 21750</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8617; 24378</t>
+          <t>8612; 24209</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5891; 19328</t>
+          <t>5980; 18984</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>7674; 30982</t>
+          <t>8153; 31085</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>13468; 31501</t>
+          <t>13551; 30902</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>11686; 29835</t>
+          <t>12337; 30485</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>18068; 39386</t>
+          <t>18062; 39000</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>17404; 54324</t>
+          <t>18837; 56427</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7662; 21632</t>
+          <t>7423; 21844</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>18583; 42998</t>
+          <t>18081; 41058</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8680; 25278</t>
+          <t>8982; 25679</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7427; 27131</t>
+          <t>6970; 26684</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>22923; 45457</t>
+          <t>22092; 43189</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18720; 39529</t>
+          <t>18128; 38322</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>36021; 61292</t>
+          <t>33709; 60040</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>29454; 66084</t>
+          <t>29693; 65486</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>34655; 61368</t>
+          <t>34233; 61055</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>40256; 71452</t>
+          <t>40435; 71275</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>48370; 80787</t>
+          <t>48856; 78396</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>45050; 83837</t>
+          <t>44243; 82273</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>17296; 36697</t>
+          <t>17512; 38060</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>26190; 51638</t>
+          <t>24486; 50010</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>26223; 50050</t>
+          <t>26277; 51776</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>34644; 62046</t>
+          <t>35773; 63522</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>19825; 42639</t>
+          <t>20111; 43451</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15401; 35246</t>
+          <t>15492; 36797</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>24851; 49985</t>
+          <t>25453; 49354</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>37858; 58680</t>
+          <t>37913; 59951</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>42475; 70756</t>
+          <t>42212; 72634</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>45483; 76998</t>
+          <t>44181; 77395</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>56921; 90835</t>
+          <t>56217; 89765</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>78834; 114359</t>
+          <t>79561; 114119</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>13178; 32895</t>
+          <t>13684; 32508</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>10292; 27639</t>
+          <t>10727; 27733</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>14755; 35569</t>
+          <t>14940; 36328</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>24952; 84846</t>
+          <t>24037; 84759</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>12261; 30944</t>
+          <t>12052; 29420</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>17221; 39013</t>
+          <t>16000; 37215</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>17285; 38675</t>
+          <t>18274; 38625</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>64170; 93577</t>
+          <t>63441; 94024</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>29785; 55366</t>
+          <t>29334; 55777</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>31264; 58863</t>
+          <t>30949; 58215</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>37444; 67686</t>
+          <t>37005; 67027</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>81653; 169949</t>
+          <t>85551; 172460</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>9265; 25518</t>
+          <t>8681; 26698</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>6198; 24124</t>
+          <t>5903; 22685</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5157; 19000</t>
+          <t>5854; 20972</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>27616; 51675</t>
+          <t>27260; 49985</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>15120; 36031</t>
+          <t>16203; 36662</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9888; 28683</t>
+          <t>9167; 27998</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>9342; 28961</t>
+          <t>9871; 28806</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>39936; 59416</t>
+          <t>39493; 58836</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>29273; 54589</t>
+          <t>29748; 54989</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>18481; 44633</t>
+          <t>18551; 43311</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>18135; 42911</t>
+          <t>18415; 40964</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>74124; 102928</t>
+          <t>71947; 103133</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 9468</t>
+          <t>0; 9627</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>4212; 18192</t>
+          <t>4037; 17695</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3511; 16643</t>
+          <t>3163; 15649</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>19834; 36076</t>
+          <t>19526; 36273</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4874; 16845</t>
+          <t>4907; 17957</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1865; 12276</t>
+          <t>1933; 14174</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5832; 22245</t>
+          <t>5202; 20776</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>9763; 38755</t>
+          <t>10284; 40209</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>6272; 20172</t>
+          <t>6212; 20910</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>8337; 25296</t>
+          <t>8111; 24739</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>12007; 30586</t>
+          <t>12037; 31963</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>24984; 68955</t>
+          <t>23360; 69569</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>956; 10467</t>
+          <t>946; 9808</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1054; 12060</t>
+          <t>1063; 14097</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 8743</t>
+          <t>0; 8065</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>5542; 15536</t>
+          <t>5221; 15212</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1143; 9500</t>
+          <t>1138; 9748</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1059; 12005</t>
+          <t>1056; 9540</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2654; 17697</t>
+          <t>2707; 16860</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>11694; 23241</t>
+          <t>11696; 23625</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3308; 16089</t>
+          <t>3223; 16319</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3262; 19353</t>
+          <t>4170; 18301</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>4477; 20440</t>
+          <t>4085; 19262</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>19503; 34281</t>
+          <t>19442; 34214</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>75537; 111272</t>
+          <t>74314; 112315</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>91137; 135348</t>
+          <t>89588; 135994</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>93270; 138724</t>
+          <t>93646; 136753</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>161243; 244335</t>
+          <t>165539; 245205</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>110874; 157521</t>
+          <t>110901; 158730</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>96570; 144198</t>
+          <t>96514; 145060</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>133323; 185772</t>
+          <t>132445; 183409</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>229379; 318533</t>
+          <t>228905; 318257</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>193013; 253601</t>
+          <t>197272; 256187</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>200265; 261234</t>
+          <t>200489; 262950</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>241127; 308326</t>
+          <t>240378; 306778</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>425087; 540954</t>
+          <t>422439; 546280</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P22$concerIndv-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P22$concerIndv-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,56%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,82; 3,07</t>
+          <t>0,8; 2,96</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,42; 2,39</t>
+          <t>0,41; 2,17</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,2; 6,34</t>
+          <t>2,34; 6,51</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,25; 8,92</t>
+          <t>1,31; 8,1</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,48; 4,65</t>
+          <t>1,58; 4,69</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,0; 5,63</t>
+          <t>2,12; 5,93</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,51; 4,8</t>
+          <t>1,49; 4,64</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,6; 9,93</t>
+          <t>2,85; 10,23</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,41; 3,22</t>
+          <t>1,44; 3,26</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,4; 3,45</t>
+          <t>1,43; 3,49</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,22; 4,79</t>
+          <t>2,25; 4,72</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,64; 7,91</t>
+          <t>2,8; 7,38</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,98%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,01; 2,98</t>
+          <t>1,01; 3,04</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,63; 5,98</t>
+          <t>2,58; 6,09</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,52; 4,35</t>
+          <t>1,51; 4,29</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,65; 6,3</t>
+          <t>1,91; 6,71</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,53; 6,9</t>
+          <t>3,65; 7,2</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,97; 6,28</t>
+          <t>3,05; 6,38</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,0; 10,69</t>
+          <t>6,31; 11,1</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,81; 12,81</t>
+          <t>7,45; 12,93</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,52; 4,49</t>
+          <t>2,47; 4,42</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3,12; 5,49</t>
+          <t>3,21; 5,59</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4,24; 6,8</t>
+          <t>4,25; 6,74</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,73; 8,8</t>
+          <t>5,36; 9,0</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,92%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,74; 5,96</t>
+          <t>2,78; 5,92</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,59; 7,33</t>
+          <t>3,75; 7,6</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,93; 7,75</t>
+          <t>3,86; 7,39</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,67; 11,84</t>
+          <t>6,52; 11,59</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,92; 6,3</t>
+          <t>2,78; 6,06</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,18; 5,18</t>
+          <t>2,12; 5,08</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,85; 7,46</t>
+          <t>3,78; 7,51</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,99; 11,05</t>
+          <t>7,26; 11,11</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,18; 5,47</t>
+          <t>3,24; 5,33</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3,17; 5,56</t>
+          <t>3,28; 5,64</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4,23; 6,75</t>
+          <t>4,21; 6,87</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7,37; 10,58</t>
+          <t>7,51; 10,72</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>10,22%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,64; 6,28</t>
+          <t>2,69; 6,35</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,75; 4,51</t>
+          <t>1,72; 4,75</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,31; 5,62</t>
+          <t>2,36; 5,61</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,71; 9,55</t>
+          <t>6,68; 11,39</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,34; 5,72</t>
+          <t>2,27; 5,68</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,6; 6,04</t>
+          <t>2,84; 6,37</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,82; 5,96</t>
+          <t>2,76; 5,98</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8,9; 13,19</t>
+          <t>9,87; 13,48</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,84; 5,4</t>
+          <t>2,82; 5,34</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,51; 4,73</t>
+          <t>2,57; 4,73</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,86; 5,18</t>
+          <t>2,99; 5,15</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5,34; 10,77</t>
+          <t>8,79; 11,65</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>8,17%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,24; 6,9</t>
+          <t>2,42; 6,81</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,37; 5,28</t>
+          <t>1,47; 5,37</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,23; 4,41</t>
+          <t>1,09; 4,09</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,86; 8,91</t>
+          <t>5,47; 9,48</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,02; 9,09</t>
+          <t>3,9; 8,81</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,05; 6,25</t>
+          <t>2,03; 6,35</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,99; 5,8</t>
+          <t>1,97; 5,89</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>7,24; 10,78</t>
+          <t>7,48; 10,96</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,77; 6,96</t>
+          <t>3,55; 7,01</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2,11; 4,94</t>
+          <t>2,11; 4,91</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,89; 4,21</t>
+          <t>1,92; 4,34</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,5; 9,32</t>
+          <t>6,85; 9,59</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>6,76%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,29</t>
+          <t>0,0; 3,06</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,3; 5,71</t>
+          <t>1,36; 6,03</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,95; 4,68</t>
+          <t>0,95; 5,0</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5,3; 9,85</t>
+          <t>5,24; 9,82</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,43; 5,24</t>
+          <t>1,49; 4,93</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,55; 4,0</t>
+          <t>0,55; 3,74</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,38; 5,52</t>
+          <t>1,71; 5,98</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,69; 6,61</t>
+          <t>4,87; 8,17</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,98; 3,29</t>
+          <t>1,0; 3,42</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1,22; 3,73</t>
+          <t>1,22; 3,74</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1,69; 4,5</t>
+          <t>1,69; 4,38</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2,39; 7,12</t>
+          <t>5,37; 8,2</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,76%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,45; 4,71</t>
+          <t>0,47; 4,55</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,43; 5,64</t>
+          <t>0,42; 5,22</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,14</t>
+          <t>0,0; 3,33</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,85; 5,38</t>
+          <t>1,67; 5,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,34; 2,92</t>
+          <t>0,34; 2,88</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,27; 2,45</t>
+          <t>0,52; 2,67</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,68; 4,23</t>
+          <t>0,65; 4,12</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,75; 5,55</t>
+          <t>2,94; 5,72</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,59; 3,01</t>
+          <t>0,61; 2,99</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,65; 2,86</t>
+          <t>0,52; 2,67</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,62; 2,94</t>
+          <t>0,61; 2,98</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,74; 4,83</t>
+          <t>2,75; 4,89</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>7,53%</t>
         </is>
       </c>
     </row>
@@ -1697,42 +1697,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,27; 3,43</t>
+          <t>2,29; 3,4</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,62; 3,97</t>
+          <t>2,64; 3,93</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,76; 4,03</t>
+          <t>2,78; 3,99</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4,78; 7,09</t>
+          <t>5,74; 7,57</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>3,28; 4,7</t>
+          <t>3,3; 4,62</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,71; 4,08</t>
+          <t>2,76; 4,01</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,74; 5,18</t>
+          <t>3,68; 5,16</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>6,25; 8,7</t>
+          <t>7,65; 9,25</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1742,17 +1742,17 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2,87; 3,76</t>
+          <t>2,89; 3,81</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3,47; 4,43</t>
+          <t>3,51; 4,45</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>5,93; 7,67</t>
+          <t>6,99; 8,1</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15594</t>
+          <t>15244</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>16650</t>
+          <t>19896</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>32245</t>
+          <t>35139</t>
         </is>
       </c>
     </row>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4066; 15116</t>
+          <t>3968; 14588</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1894; 10812</t>
+          <t>1851; 9812</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9201; 26461</t>
+          <t>9768; 27185</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5013; 35670</t>
+          <t>5326; 33029</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>6929; 21750</t>
+          <t>7373; 21922</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8612; 24209</t>
+          <t>9107; 25511</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5980; 18984</t>
+          <t>5894; 18373</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>8153; 31085</t>
+          <t>10348; 37086</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>13551; 30902</t>
+          <t>13869; 31328</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>12337; 30485</t>
+          <t>12661; 30829</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>18062; 39000</t>
+          <t>18276; 38356</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>18837; 56427</t>
+          <t>21548; 56843</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>14701</t>
+          <t>17924</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>47885</t>
+          <t>50230</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>62587</t>
+          <t>68154</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7423; 21844</t>
+          <t>7432; 22252</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>18081; 41058</t>
+          <t>17726; 41873</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8982; 25679</t>
+          <t>8934; 25336</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6970; 26684</t>
+          <t>9115; 32016</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>22092; 43189</t>
+          <t>22842; 45012</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18128; 38322</t>
+          <t>18586; 38949</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>33709; 60040</t>
+          <t>35453; 62330</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>29693; 65486</t>
+          <t>37241; 64677</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>34233; 61055</t>
+          <t>33561; 60042</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>40435; 71275</t>
+          <t>41612; 72571</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>48856; 78396</t>
+          <t>48944; 77709</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>44243; 82273</t>
+          <t>52326; 87900</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>46693</t>
+          <t>54669</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>48137</t>
+          <t>56237</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>94830</t>
+          <t>110907</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>17512; 38060</t>
+          <t>17763; 37808</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>24486; 50010</t>
+          <t>25569; 51801</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>26277; 51776</t>
+          <t>25759; 49396</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>35773; 63522</t>
+          <t>40482; 71947</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>20111; 43451</t>
+          <t>19200; 41824</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15492; 36797</t>
+          <t>15047; 36079</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>25453; 49354</t>
+          <t>24989; 49663</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>37913; 59951</t>
+          <t>45154; 69105</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>42212; 72634</t>
+          <t>43048; 70861</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>44181; 77395</t>
+          <t>45680; 78493</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>56217; 89765</t>
+          <t>56024; 91364</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>79561; 114119</t>
+          <t>93292; 133276</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>56341</t>
+          <t>60840</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>80005</t>
+          <t>86030</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>136346</t>
+          <t>146870</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>13684; 32508</t>
+          <t>13925; 32904</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>10727; 27733</t>
+          <t>10567; 29195</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>14940; 36328</t>
+          <t>15241; 36261</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>24037; 84759</t>
+          <t>46828; 79771</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>12052; 29420</t>
+          <t>11659; 29231</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>16000; 37215</t>
+          <t>17515; 39233</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>18274; 38625</t>
+          <t>17893; 38751</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>63441; 94024</t>
+          <t>72757; 99352</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>29334; 55777</t>
+          <t>29164; 55154</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>30949; 58215</t>
+          <t>31642; 58273</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>37005; 67027</t>
+          <t>38753; 66596</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>85551; 172460</t>
+          <t>126329; 167413</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>37889</t>
+          <t>44236</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>48840</t>
+          <t>55276</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>86729</t>
+          <t>99512</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>8681; 26698</t>
+          <t>9355; 26344</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>5903; 22685</t>
+          <t>6307; 23058</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5854; 20972</t>
+          <t>5186; 19472</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>27260; 49985</t>
+          <t>33334; 57794</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>16203; 36662</t>
+          <t>15733; 35504</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9167; 27998</t>
+          <t>9076; 28430</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>9871; 28806</t>
+          <t>9768; 29288</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>39493; 58836</t>
+          <t>45517; 66626</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>29748; 54989</t>
+          <t>28009; 55374</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>18551; 43311</t>
+          <t>18482; 43030</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>18415; 40964</t>
+          <t>18696; 42193</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>71947; 103133</t>
+          <t>83453; 116748</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>26711</t>
+          <t>29609</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>23915</t>
+          <t>27619</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>50626</t>
+          <t>57228</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 9627</t>
+          <t>0; 8938</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>4037; 17695</t>
+          <t>4212; 18681</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3163; 15649</t>
+          <t>3190; 16710</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>19526; 36273</t>
+          <t>21331; 39975</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4907; 17957</t>
+          <t>5123; 16921</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1933; 14174</t>
+          <t>1931; 13253</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5202; 20776</t>
+          <t>6430; 22478</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>10284; 40209</t>
+          <t>21386; 35876</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>6212; 20910</t>
+          <t>6365; 21760</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>8111; 24739</t>
+          <t>8094; 24804</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>12037; 31963</t>
+          <t>11980; 31103</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>23360; 69569</t>
+          <t>45430; 69429</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>9428</t>
+          <t>9623</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>16765</t>
+          <t>19481</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>26192</t>
+          <t>29105</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>946; 9808</t>
+          <t>968; 9471</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1063; 14097</t>
+          <t>1058; 13034</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 8065</t>
+          <t>0; 8564</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>5221; 15212</t>
+          <t>5177; 15501</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1138; 9748</t>
+          <t>1134; 9608</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1056; 9540</t>
+          <t>2040; 10395</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2707; 16860</t>
+          <t>2574; 16446</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>11696; 23625</t>
+          <t>13672; 26593</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3223; 16319</t>
+          <t>3320; 16185</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>4170; 18301</t>
+          <t>3298; 17050</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>4085; 19262</t>
+          <t>3990; 19541</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>19442; 34214</t>
+          <t>21300; 37882</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>207358</t>
+          <t>232146</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>282196</t>
+          <t>314769</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>489554</t>
+          <t>546915</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>74314; 112315</t>
+          <t>74994; 111322</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>89588; 135994</t>
+          <t>90345; 134649</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>93646; 136753</t>
+          <t>94356; 135245</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>165539; 245205</t>
+          <t>202795; 267343</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>110901; 158730</t>
+          <t>111302; 156032</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>96514; 145060</t>
+          <t>98099; 142696</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>132445; 183409</t>
+          <t>130180; 182601</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>228905; 318257</t>
+          <t>285695; 345363</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>197272; 256187</t>
+          <t>197741; 255619</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>200489; 262950</t>
+          <t>202108; 266053</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>240378; 306778</t>
+          <t>243048; 308286</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>422439; 546280</t>
+          <t>507717; 588258</t>
         </is>
       </c>
     </row>
